--- a/Distribucion/Excels/EDRD.xlsx
+++ b/Distribucion/Excels/EDRD.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -534,7 +534,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -666,7 +666,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -765,7 +765,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -897,7 +897,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -930,7 +930,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1029,7 +1029,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1062,7 +1062,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1128,7 +1128,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1293,7 +1293,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1326,7 +1326,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1392,7 +1392,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1425,7 +1425,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1458,7 +1458,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1524,7 +1524,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1590,7 +1590,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1656,7 +1656,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1689,7 +1689,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1788,7 +1788,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1920,7 +1920,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1986,7 +1986,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2019,7 +2019,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2052,7 +2052,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2085,7 +2085,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2118,7 +2118,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2151,7 +2151,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2250,7 +2250,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2283,7 +2283,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2316,7 +2316,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2349,7 +2349,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2382,7 +2382,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2448,7 +2448,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2547,7 +2547,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2580,7 +2580,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2679,7 +2679,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2712,7 +2712,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2811,7 +2811,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2844,7 +2844,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2877,7 +2877,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2910,7 +2910,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2943,7 +2943,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2976,7 +2976,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3009,7 +3009,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3042,7 +3042,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3075,7 +3075,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3108,7 +3108,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3141,7 +3141,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3174,7 +3174,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3207,7 +3207,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3240,7 +3240,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3273,7 +3273,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3339,7 +3339,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3372,7 +3372,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3438,7 +3438,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3504,7 +3504,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3537,7 +3537,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3570,7 +3570,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3603,7 +3603,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3636,7 +3636,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3702,7 +3702,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3735,7 +3735,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3768,7 +3768,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3801,7 +3801,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3834,7 +3834,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3900,7 +3900,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3933,7 +3933,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3966,7 +3966,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3999,7 +3999,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4032,7 +4032,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4065,7 +4065,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4098,7 +4098,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4131,7 +4131,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4164,7 +4164,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4197,7 +4197,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4230,7 +4230,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4263,7 +4263,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4329,7 +4329,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4362,7 +4362,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4395,7 +4395,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4461,7 +4461,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4494,7 +4494,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4527,7 +4527,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4593,7 +4593,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4626,7 +4626,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4692,7 +4692,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4725,7 +4725,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4791,7 +4791,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4824,7 +4824,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4890,7 +4890,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4956,7 +4956,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5022,7 +5022,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5055,7 +5055,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5121,7 +5121,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5154,7 +5154,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5187,7 +5187,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5220,7 +5220,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5286,7 +5286,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5385,7 +5385,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5418,7 +5418,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5484,7 +5484,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5517,7 +5517,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5583,7 +5583,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5616,7 +5616,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5649,7 +5649,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5715,7 +5715,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5748,7 +5748,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5781,7 +5781,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5814,7 +5814,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5847,7 +5847,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5880,7 +5880,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5946,7 +5946,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5979,7 +5979,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6012,7 +6012,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6078,7 +6078,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6111,7 +6111,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6144,7 +6144,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6177,7 +6177,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6243,7 +6243,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6276,7 +6276,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6309,7 +6309,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6375,7 +6375,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6408,7 +6408,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6441,7 +6441,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6474,7 +6474,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6540,7 +6540,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6573,7 +6573,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6606,7 +6606,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6705,7 +6705,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6738,7 +6738,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6837,7 +6837,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6870,7 +6870,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6903,7 +6903,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6936,7 +6936,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7002,7 +7002,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7035,7 +7035,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7068,7 +7068,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7134,7 +7134,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7167,7 +7167,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7200,7 +7200,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7233,7 +7233,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7266,7 +7266,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7299,7 +7299,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7332,7 +7332,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7398,7 +7398,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7431,7 +7431,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7497,7 +7497,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7530,7 +7530,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7563,7 +7563,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7596,7 +7596,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7629,7 +7629,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7695,7 +7695,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7728,7 +7728,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7761,7 +7761,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7794,7 +7794,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7860,7 +7860,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7893,7 +7893,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7926,7 +7926,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7959,7 +7959,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7992,7 +7992,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -8025,7 +8025,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -8058,7 +8058,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -8091,7 +8091,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -8124,7 +8124,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -8157,7 +8157,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -8190,7 +8190,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -8256,7 +8256,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -8289,7 +8289,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -8322,7 +8322,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -8355,7 +8355,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -8388,7 +8388,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -8421,7 +8421,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -8454,7 +8454,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -8487,7 +8487,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -8520,7 +8520,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -8553,7 +8553,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -8586,7 +8586,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -8619,7 +8619,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -8652,7 +8652,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -8685,7 +8685,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -8718,7 +8718,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -8751,7 +8751,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -8784,7 +8784,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -8817,7 +8817,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -8850,7 +8850,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -8883,7 +8883,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -8916,7 +8916,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -8949,7 +8949,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -8982,7 +8982,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -9015,7 +9015,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -9048,7 +9048,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -9081,7 +9081,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -9114,7 +9114,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -9147,7 +9147,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -9180,7 +9180,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -9246,7 +9246,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -9279,7 +9279,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -9312,7 +9312,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -9345,7 +9345,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -9378,7 +9378,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -9411,7 +9411,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -9444,7 +9444,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -9477,7 +9477,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -9510,7 +9510,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -9543,7 +9543,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -9576,7 +9576,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -9609,7 +9609,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -9642,7 +9642,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -9675,7 +9675,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -9708,7 +9708,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -9741,7 +9741,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -9774,7 +9774,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -9807,7 +9807,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -9840,7 +9840,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -9873,7 +9873,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -9906,7 +9906,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -9939,7 +9939,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -9972,7 +9972,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10005,7 +10005,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10038,7 +10038,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -10071,7 +10071,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -10104,7 +10104,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -10137,7 +10137,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -10170,7 +10170,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -10203,7 +10203,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -10236,7 +10236,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -10269,7 +10269,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -10302,7 +10302,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -10335,7 +10335,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -10368,7 +10368,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -10401,7 +10401,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -10434,7 +10434,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -10467,7 +10467,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -10500,7 +10500,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -10533,7 +10533,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -10566,7 +10566,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -10599,7 +10599,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -10632,7 +10632,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -10665,7 +10665,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -10698,7 +10698,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -10731,7 +10731,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -10764,7 +10764,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -10797,7 +10797,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -10830,7 +10830,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -10863,7 +10863,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -10896,7 +10896,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -10929,7 +10929,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -10962,7 +10962,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -10995,7 +10995,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -11028,7 +11028,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11094,7 +11094,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11127,7 +11127,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -11160,7 +11160,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -11193,7 +11193,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11226,7 +11226,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -11325,7 +11325,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11358,7 +11358,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11391,7 +11391,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11424,7 +11424,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11490,7 +11490,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11523,7 +11523,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11556,7 +11556,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -11589,7 +11589,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11622,7 +11622,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11655,7 +11655,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11688,7 +11688,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11721,7 +11721,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -11754,7 +11754,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -11787,7 +11787,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -11820,7 +11820,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -11853,7 +11853,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -11886,7 +11886,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11919,7 +11919,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11952,7 +11952,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -11985,7 +11985,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -12018,7 +12018,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12051,7 +12051,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12084,7 +12084,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12117,7 +12117,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -12183,7 +12183,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -12249,7 +12249,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -12282,7 +12282,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -12315,7 +12315,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -12348,7 +12348,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -12381,7 +12381,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -12414,7 +12414,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -12480,7 +12480,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -12513,7 +12513,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -12546,7 +12546,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -12579,7 +12579,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -12612,7 +12612,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -12645,7 +12645,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -12678,7 +12678,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -12711,7 +12711,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -12744,7 +12744,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -12777,7 +12777,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -12810,7 +12810,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -12843,7 +12843,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -12876,7 +12876,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -12909,7 +12909,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -12942,7 +12942,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -12975,7 +12975,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -13008,7 +13008,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -13041,7 +13041,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -13074,7 +13074,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -13107,7 +13107,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -13140,7 +13140,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -13173,7 +13173,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -13206,7 +13206,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -13239,7 +13239,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -13272,7 +13272,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -13305,7 +13305,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -13371,7 +13371,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -13404,7 +13404,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -13437,7 +13437,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -13470,7 +13470,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -13503,7 +13503,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -13536,7 +13536,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -13569,7 +13569,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -13635,7 +13635,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -13668,7 +13668,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -13701,7 +13701,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -13734,7 +13734,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -13767,7 +13767,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -13800,7 +13800,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -13833,7 +13833,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -13866,7 +13866,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -13899,7 +13899,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -13932,7 +13932,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -13965,7 +13965,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -13998,7 +13998,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -14031,7 +14031,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -14064,7 +14064,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -14097,7 +14097,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -14130,7 +14130,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -14163,7 +14163,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -14196,7 +14196,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -14229,7 +14229,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -14262,7 +14262,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -14295,7 +14295,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -14328,7 +14328,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -14361,7 +14361,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -14394,7 +14394,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -14427,7 +14427,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -14460,7 +14460,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -14526,7 +14526,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -14559,7 +14559,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -14592,7 +14592,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -14625,7 +14625,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -14658,7 +14658,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -14691,7 +14691,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -14724,7 +14724,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14757,7 +14757,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>01 - Andalucía</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -14790,7 +14790,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -14823,7 +14823,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -14856,7 +14856,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -14889,7 +14889,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -14922,7 +14922,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -14955,7 +14955,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -14988,7 +14988,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -15021,7 +15021,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -15054,7 +15054,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -15087,7 +15087,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -15120,7 +15120,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -15153,7 +15153,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -15186,7 +15186,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -15252,7 +15252,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -15285,7 +15285,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -15318,7 +15318,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -15351,7 +15351,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -15384,7 +15384,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -15417,7 +15417,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -15450,7 +15450,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -15483,7 +15483,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -15516,7 +15516,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -15549,7 +15549,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -15582,7 +15582,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -15615,7 +15615,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -15648,7 +15648,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -15681,7 +15681,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -15714,7 +15714,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -15747,7 +15747,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -15780,7 +15780,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -15813,7 +15813,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -15846,7 +15846,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -15879,7 +15879,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -15912,7 +15912,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -15945,7 +15945,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -15978,7 +15978,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16011,7 +16011,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16044,7 +16044,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16077,7 +16077,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16110,7 +16110,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16143,7 +16143,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16176,7 +16176,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16209,7 +16209,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16242,7 +16242,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16275,7 +16275,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16308,7 +16308,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16341,7 +16341,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16374,7 +16374,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16407,7 +16407,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16440,7 +16440,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16473,7 +16473,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16506,7 +16506,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16539,7 +16539,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -16572,7 +16572,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16605,7 +16605,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16638,7 +16638,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16671,7 +16671,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16704,7 +16704,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16737,7 +16737,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16770,7 +16770,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -16803,7 +16803,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -16836,7 +16836,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -16869,7 +16869,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -16902,7 +16902,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -16935,7 +16935,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -16968,7 +16968,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17001,7 +17001,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17034,7 +17034,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17067,7 +17067,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17100,7 +17100,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17133,7 +17133,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17166,7 +17166,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17199,7 +17199,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17232,7 +17232,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17265,7 +17265,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17298,7 +17298,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17331,7 +17331,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17364,7 +17364,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17397,7 +17397,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17430,7 +17430,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17463,7 +17463,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17496,7 +17496,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17529,7 +17529,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17562,7 +17562,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17595,7 +17595,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17628,7 +17628,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17661,7 +17661,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17727,7 +17727,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17760,7 +17760,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17793,7 +17793,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17826,7 +17826,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17859,7 +17859,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17892,7 +17892,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17925,7 +17925,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17958,7 +17958,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17991,7 +17991,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -18024,7 +18024,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -18057,7 +18057,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -18090,7 +18090,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -18123,7 +18123,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -18156,7 +18156,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -18189,7 +18189,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -18222,7 +18222,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18255,7 +18255,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18288,7 +18288,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18321,7 +18321,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -18354,7 +18354,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18387,7 +18387,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18420,7 +18420,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18453,7 +18453,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18486,7 +18486,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18519,7 +18519,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18552,7 +18552,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18585,7 +18585,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18618,7 +18618,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18651,7 +18651,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18684,7 +18684,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18717,7 +18717,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18750,7 +18750,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18783,7 +18783,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18816,7 +18816,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18849,7 +18849,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18882,7 +18882,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18915,7 +18915,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18948,7 +18948,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18981,7 +18981,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -19014,7 +19014,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -19047,7 +19047,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -19080,7 +19080,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -19113,7 +19113,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -19146,7 +19146,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -19179,7 +19179,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -19212,7 +19212,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -19245,7 +19245,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -19278,7 +19278,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -19311,7 +19311,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -19344,7 +19344,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -19377,7 +19377,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -19410,7 +19410,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -19443,7 +19443,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -19476,7 +19476,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -19509,7 +19509,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -19542,7 +19542,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -19575,7 +19575,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -19608,7 +19608,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -19641,7 +19641,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -19674,7 +19674,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -19707,7 +19707,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -19740,7 +19740,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -19773,7 +19773,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -19806,7 +19806,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -19839,7 +19839,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -19872,7 +19872,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -19905,7 +19905,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -19938,7 +19938,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -19971,7 +19971,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -20004,7 +20004,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -20037,7 +20037,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -20070,7 +20070,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -20103,7 +20103,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -20136,7 +20136,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -20169,7 +20169,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -20202,7 +20202,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -20235,7 +20235,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -20268,7 +20268,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -20301,7 +20301,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -20334,7 +20334,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -20367,7 +20367,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -20400,7 +20400,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -20433,7 +20433,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -20466,7 +20466,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -20499,7 +20499,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -20532,7 +20532,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -20565,7 +20565,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -20598,7 +20598,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -20631,7 +20631,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -20664,7 +20664,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -20697,7 +20697,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -20730,7 +20730,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -20763,7 +20763,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -20796,7 +20796,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -20829,7 +20829,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -20862,7 +20862,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -20895,7 +20895,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -20928,7 +20928,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -20961,7 +20961,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -20994,7 +20994,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -21027,7 +21027,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -21060,7 +21060,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -21093,7 +21093,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -21126,7 +21126,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -21159,7 +21159,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -21192,7 +21192,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -21225,7 +21225,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -21258,7 +21258,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -21291,7 +21291,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -21324,7 +21324,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -21357,7 +21357,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -21390,7 +21390,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -21423,7 +21423,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -21456,7 +21456,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -21489,7 +21489,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -21522,7 +21522,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -21555,7 +21555,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -21588,7 +21588,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -21621,7 +21621,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -21654,7 +21654,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -21687,7 +21687,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -21720,7 +21720,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -21753,7 +21753,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -21786,7 +21786,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -21819,7 +21819,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -21852,7 +21852,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -21885,7 +21885,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -21918,7 +21918,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -21951,7 +21951,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -21984,7 +21984,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -22017,7 +22017,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -22050,7 +22050,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -22083,7 +22083,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -22116,7 +22116,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -22149,7 +22149,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -22182,7 +22182,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -22215,7 +22215,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -22248,7 +22248,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -22281,7 +22281,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -22314,7 +22314,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -22347,7 +22347,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -22380,7 +22380,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -22413,7 +22413,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -22446,7 +22446,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -22479,7 +22479,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -22512,7 +22512,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -22545,7 +22545,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -22578,7 +22578,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -22611,7 +22611,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -22644,7 +22644,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -22677,7 +22677,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>02 - Aragón</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -22710,7 +22710,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -22743,7 +22743,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -22776,7 +22776,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -22809,7 +22809,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -22842,7 +22842,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -22875,7 +22875,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -22908,7 +22908,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -22941,7 +22941,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -22974,7 +22974,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -23007,7 +23007,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -23040,7 +23040,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -23073,7 +23073,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -23106,7 +23106,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -23139,7 +23139,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -23172,7 +23172,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -23205,7 +23205,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -23238,7 +23238,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -23271,7 +23271,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -23304,7 +23304,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -23337,7 +23337,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -23370,7 +23370,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -23403,7 +23403,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -23436,7 +23436,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -23469,7 +23469,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -23502,7 +23502,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -23535,7 +23535,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -23568,7 +23568,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -23601,7 +23601,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -23634,7 +23634,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -23667,7 +23667,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -23700,7 +23700,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -23733,7 +23733,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -23766,7 +23766,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -23799,7 +23799,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -23832,7 +23832,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -23865,7 +23865,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -23898,7 +23898,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -23931,7 +23931,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -23964,7 +23964,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -23997,7 +23997,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -24030,7 +24030,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -24063,7 +24063,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -24096,7 +24096,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -24129,7 +24129,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>04 - Illes Balears</t>
+          <t>Illes Balears</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -24162,7 +24162,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -24195,7 +24195,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -24228,7 +24228,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -24261,7 +24261,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -24294,7 +24294,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -24327,7 +24327,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -24360,7 +24360,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -24393,7 +24393,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -24426,7 +24426,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -24459,7 +24459,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -24492,7 +24492,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -24525,7 +24525,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -24558,7 +24558,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -24591,7 +24591,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -24624,7 +24624,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -24657,7 +24657,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -24690,7 +24690,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -24723,7 +24723,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -24756,7 +24756,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -24789,7 +24789,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -24822,7 +24822,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -24855,7 +24855,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -24888,7 +24888,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -24921,7 +24921,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -24954,7 +24954,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -24987,7 +24987,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -25020,7 +25020,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -25053,7 +25053,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -25086,7 +25086,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -25119,7 +25119,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -25152,7 +25152,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -25185,7 +25185,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -25218,7 +25218,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -25251,7 +25251,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -25284,7 +25284,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -25317,7 +25317,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -25350,7 +25350,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -25383,7 +25383,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -25416,7 +25416,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -25449,7 +25449,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -25482,7 +25482,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -25515,7 +25515,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -25548,7 +25548,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -25581,7 +25581,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>05 - Canarias</t>
+          <t>Canarias</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -25614,7 +25614,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -25647,7 +25647,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -25680,7 +25680,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -25713,7 +25713,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -25746,7 +25746,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -25779,7 +25779,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -25812,7 +25812,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -25845,7 +25845,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -25878,7 +25878,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -25911,7 +25911,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -25944,7 +25944,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -25977,7 +25977,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -26010,7 +26010,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -26043,7 +26043,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>07 - C.León</t>
+          <t>C.León</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -26076,7 +26076,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>08 - C.La Mancha</t>
+          <t>C.La Mancha</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -26109,7 +26109,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>08 - C.La Mancha</t>
+          <t>C.La Mancha</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -26142,7 +26142,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>08 - C.La Mancha</t>
+          <t>C.La Mancha</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -26175,7 +26175,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -26208,7 +26208,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -26241,7 +26241,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -26274,7 +26274,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -26307,7 +26307,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -26340,7 +26340,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -26373,7 +26373,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -26406,7 +26406,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -26439,7 +26439,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -26472,7 +26472,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -26505,7 +26505,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -26538,7 +26538,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -26571,7 +26571,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -26604,7 +26604,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -26637,7 +26637,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -26670,7 +26670,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -26703,7 +26703,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -26736,7 +26736,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -26769,7 +26769,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -26802,7 +26802,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -26835,7 +26835,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
@@ -26868,7 +26868,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
@@ -26901,7 +26901,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
@@ -26934,7 +26934,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
@@ -26967,7 +26967,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
@@ -27000,7 +27000,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
@@ -27033,7 +27033,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
@@ -27066,7 +27066,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -27099,7 +27099,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -27132,7 +27132,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
@@ -27165,7 +27165,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
@@ -27198,7 +27198,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
@@ -27231,7 +27231,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
@@ -27264,7 +27264,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
@@ -27297,7 +27297,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
@@ -27330,7 +27330,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
@@ -27363,7 +27363,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
@@ -27396,7 +27396,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
@@ -27429,7 +27429,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
@@ -27462,7 +27462,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
@@ -27495,7 +27495,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
@@ -27528,7 +27528,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
@@ -27561,7 +27561,7 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
@@ -27594,7 +27594,7 @@
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
@@ -27627,7 +27627,7 @@
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
@@ -27660,7 +27660,7 @@
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
@@ -27693,7 +27693,7 @@
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
@@ -27726,7 +27726,7 @@
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
@@ -27759,7 +27759,7 @@
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
@@ -27792,7 +27792,7 @@
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
@@ -27825,7 +27825,7 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
@@ -27858,7 +27858,7 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
@@ -27891,7 +27891,7 @@
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
@@ -27924,7 +27924,7 @@
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
@@ -27957,7 +27957,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
@@ -27990,7 +27990,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
@@ -28023,7 +28023,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B837" t="inlineStr">
@@ -28056,7 +28056,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B838" t="inlineStr">
@@ -28089,7 +28089,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B839" t="inlineStr">
@@ -28122,7 +28122,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B840" t="inlineStr">
@@ -28155,7 +28155,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B841" t="inlineStr">
@@ -28188,7 +28188,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
@@ -28221,7 +28221,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
@@ -28254,7 +28254,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
@@ -28287,7 +28287,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
@@ -28320,7 +28320,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
@@ -28353,7 +28353,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
@@ -28386,7 +28386,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
@@ -28419,7 +28419,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -28452,7 +28452,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -28485,7 +28485,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
@@ -28518,7 +28518,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
@@ -28551,7 +28551,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
@@ -28584,7 +28584,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
@@ -28617,7 +28617,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
@@ -28650,7 +28650,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
@@ -28683,7 +28683,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
@@ -28716,7 +28716,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -28749,7 +28749,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -28782,7 +28782,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -28815,7 +28815,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -28848,7 +28848,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -28881,7 +28881,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -28914,7 +28914,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
@@ -28947,7 +28947,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -28980,7 +28980,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -29013,7 +29013,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -29046,7 +29046,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -29079,7 +29079,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -29112,7 +29112,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
@@ -29145,7 +29145,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -29178,7 +29178,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -29211,7 +29211,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -29244,7 +29244,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -29277,7 +29277,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -29310,7 +29310,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -29343,7 +29343,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
@@ -29376,7 +29376,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -29409,7 +29409,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -29442,7 +29442,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -29475,7 +29475,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -29508,7 +29508,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -29541,7 +29541,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -29574,7 +29574,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -29607,7 +29607,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -29640,7 +29640,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -29673,7 +29673,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -29706,7 +29706,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -29739,7 +29739,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -29772,7 +29772,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -29805,7 +29805,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -29838,7 +29838,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -29871,7 +29871,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -29904,7 +29904,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -29937,7 +29937,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -29970,7 +29970,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -30003,7 +30003,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -30036,7 +30036,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -30069,7 +30069,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -30102,7 +30102,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -30135,7 +30135,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -30168,7 +30168,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -30201,7 +30201,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -30234,7 +30234,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -30267,7 +30267,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -30300,7 +30300,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -30333,7 +30333,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -30366,7 +30366,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -30399,7 +30399,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -30432,7 +30432,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -30465,7 +30465,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -30498,7 +30498,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -30531,7 +30531,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -30564,7 +30564,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -30597,7 +30597,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -30630,7 +30630,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -30663,7 +30663,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -30696,7 +30696,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -30729,7 +30729,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -30762,7 +30762,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -30795,7 +30795,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -30828,7 +30828,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -30861,7 +30861,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -30894,7 +30894,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -30927,7 +30927,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -30960,7 +30960,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -30993,7 +30993,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -31026,7 +31026,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -31059,7 +31059,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -31092,7 +31092,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -31125,7 +31125,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -31158,7 +31158,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -31191,7 +31191,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -31224,7 +31224,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
@@ -31257,7 +31257,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -31290,7 +31290,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
@@ -31323,7 +31323,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
@@ -31356,7 +31356,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -31389,7 +31389,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -31422,7 +31422,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -31455,7 +31455,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -31488,7 +31488,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -31521,7 +31521,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -31554,7 +31554,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -31587,7 +31587,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -31620,7 +31620,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -31653,7 +31653,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -31686,7 +31686,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
@@ -31719,7 +31719,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -31752,7 +31752,7 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
@@ -31785,7 +31785,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -31818,7 +31818,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -31851,7 +31851,7 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
@@ -31884,7 +31884,7 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
@@ -31917,7 +31917,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B955" t="inlineStr">
@@ -31950,7 +31950,7 @@
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B956" t="inlineStr">
@@ -31983,7 +31983,7 @@
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B957" t="inlineStr">
@@ -32016,7 +32016,7 @@
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B958" t="inlineStr">
@@ -32049,7 +32049,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B959" t="inlineStr">
@@ -32082,7 +32082,7 @@
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B960" t="inlineStr">
@@ -32115,7 +32115,7 @@
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B961" t="inlineStr">
@@ -32148,7 +32148,7 @@
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B962" t="inlineStr">
@@ -32181,7 +32181,7 @@
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B963" t="inlineStr">
@@ -32214,7 +32214,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B964" t="inlineStr">
@@ -32247,7 +32247,7 @@
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B965" t="inlineStr">
@@ -32280,7 +32280,7 @@
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B966" t="inlineStr">
@@ -32313,7 +32313,7 @@
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B967" t="inlineStr">
@@ -32346,7 +32346,7 @@
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B968" t="inlineStr">
@@ -32379,7 +32379,7 @@
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B969" t="inlineStr">
@@ -32412,7 +32412,7 @@
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B970" t="inlineStr">
@@ -32445,7 +32445,7 @@
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B971" t="inlineStr">
@@ -32478,7 +32478,7 @@
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B972" t="inlineStr">
@@ -32511,7 +32511,7 @@
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B973" t="inlineStr">
@@ -32544,7 +32544,7 @@
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B974" t="inlineStr">
@@ -32577,7 +32577,7 @@
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B975" t="inlineStr">
@@ -32610,7 +32610,7 @@
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>09 - Catalunya</t>
+          <t>Catalunya</t>
         </is>
       </c>
       <c r="B976" t="inlineStr">
@@ -32643,7 +32643,7 @@
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B977" t="inlineStr">
@@ -32676,7 +32676,7 @@
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B978" t="inlineStr">
@@ -32709,7 +32709,7 @@
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B979" t="inlineStr">
@@ -32742,7 +32742,7 @@
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B980" t="inlineStr">
@@ -32775,7 +32775,7 @@
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B981" t="inlineStr">
@@ -32808,7 +32808,7 @@
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B982" t="inlineStr">
@@ -32841,7 +32841,7 @@
     <row r="983">
       <c r="A983" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B983" t="inlineStr">
@@ -32874,7 +32874,7 @@
     <row r="984">
       <c r="A984" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B984" t="inlineStr">
@@ -32907,7 +32907,7 @@
     <row r="985">
       <c r="A985" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B985" t="inlineStr">
@@ -32940,7 +32940,7 @@
     <row r="986">
       <c r="A986" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B986" t="inlineStr">
@@ -32973,7 +32973,7 @@
     <row r="987">
       <c r="A987" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B987" t="inlineStr">
@@ -33006,7 +33006,7 @@
     <row r="988">
       <c r="A988" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B988" t="inlineStr">
@@ -33039,7 +33039,7 @@
     <row r="989">
       <c r="A989" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B989" t="inlineStr">
@@ -33072,7 +33072,7 @@
     <row r="990">
       <c r="A990" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B990" t="inlineStr">
@@ -33105,7 +33105,7 @@
     <row r="991">
       <c r="A991" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B991" t="inlineStr">
@@ -33138,7 +33138,7 @@
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B992" t="inlineStr">
@@ -33171,7 +33171,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B993" t="inlineStr">
@@ -33204,7 +33204,7 @@
     <row r="994">
       <c r="A994" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B994" t="inlineStr">
@@ -33237,7 +33237,7 @@
     <row r="995">
       <c r="A995" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B995" t="inlineStr">
@@ -33270,7 +33270,7 @@
     <row r="996">
       <c r="A996" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B996" t="inlineStr">
@@ -33303,7 +33303,7 @@
     <row r="997">
       <c r="A997" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B997" t="inlineStr">
@@ -33336,7 +33336,7 @@
     <row r="998">
       <c r="A998" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B998" t="inlineStr">
@@ -33369,7 +33369,7 @@
     <row r="999">
       <c r="A999" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B999" t="inlineStr">
@@ -33402,7 +33402,7 @@
     <row r="1000">
       <c r="A1000" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1000" t="inlineStr">
@@ -33435,7 +33435,7 @@
     <row r="1001">
       <c r="A1001" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1001" t="inlineStr">
@@ -33468,7 +33468,7 @@
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1002" t="inlineStr">
@@ -33501,7 +33501,7 @@
     <row r="1003">
       <c r="A1003" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1003" t="inlineStr">
@@ -33534,7 +33534,7 @@
     <row r="1004">
       <c r="A1004" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1004" t="inlineStr">
@@ -33567,7 +33567,7 @@
     <row r="1005">
       <c r="A1005" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1005" t="inlineStr">
@@ -33600,7 +33600,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -33633,7 +33633,7 @@
     <row r="1007">
       <c r="A1007" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1007" t="inlineStr">
@@ -33666,7 +33666,7 @@
     <row r="1008">
       <c r="A1008" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1008" t="inlineStr">
@@ -33699,7 +33699,7 @@
     <row r="1009">
       <c r="A1009" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1009" t="inlineStr">
@@ -33732,7 +33732,7 @@
     <row r="1010">
       <c r="A1010" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1010" t="inlineStr">
@@ -33765,7 +33765,7 @@
     <row r="1011">
       <c r="A1011" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1011" t="inlineStr">
@@ -33798,7 +33798,7 @@
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1012" t="inlineStr">
@@ -33831,7 +33831,7 @@
     <row r="1013">
       <c r="A1013" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1013" t="inlineStr">
@@ -33864,7 +33864,7 @@
     <row r="1014">
       <c r="A1014" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1014" t="inlineStr">
@@ -33897,7 +33897,7 @@
     <row r="1015">
       <c r="A1015" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1015" t="inlineStr">
@@ -33930,7 +33930,7 @@
     <row r="1016">
       <c r="A1016" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1016" t="inlineStr">
@@ -33963,7 +33963,7 @@
     <row r="1017">
       <c r="A1017" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1017" t="inlineStr">
@@ -33996,7 +33996,7 @@
     <row r="1018">
       <c r="A1018" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1018" t="inlineStr">
@@ -34029,7 +34029,7 @@
     <row r="1019">
       <c r="A1019" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1019" t="inlineStr">
@@ -34062,7 +34062,7 @@
     <row r="1020">
       <c r="A1020" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1020" t="inlineStr">
@@ -34095,7 +34095,7 @@
     <row r="1021">
       <c r="A1021" t="inlineStr">
         <is>
-          <t>11 - Extremadura</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="B1021" t="inlineStr">
@@ -34128,7 +34128,7 @@
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
-          <t>12 - Galicia</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="B1022" t="inlineStr">
@@ -34161,7 +34161,7 @@
     <row r="1023">
       <c r="A1023" t="inlineStr">
         <is>
-          <t>12 - Galicia</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="B1023" t="inlineStr">
@@ -34194,7 +34194,7 @@
     <row r="1024">
       <c r="A1024" t="inlineStr">
         <is>
-          <t>12 - Galicia</t>
+          <t>Galicia</t>
         </is>
       </c>
       <c r="B1024" t="inlineStr">
@@ -34227,7 +34227,7 @@
     <row r="1025">
       <c r="A1025" t="inlineStr">
         <is>
-          <t>15 - Navarra</t>
+          <t>Navarra</t>
         </is>
       </c>
       <c r="B1025" t="inlineStr">
